--- a/import_template_product_variant/data/template_product_variant.xlsx
+++ b/import_template_product_variant/data/template_product_variant.xlsx
@@ -61,10 +61,10 @@
     <t xml:space="preserve">*TMPL*invoice_policy</t>
   </si>
   <si>
-    <t xml:space="preserve">*TMPL*image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">image_variant</t>
+    <t xml:space="preserve">*TMPL*image_1920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image_variant_1920</t>
   </si>
   <si>
     <t xml:space="preserve">*TMPL*description_sale</t>
@@ -130,7 +130,7 @@
     <t xml:space="preserve">Description for suppliers.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit(s)</t>
+    <t xml:space="preserve">Units</t>
   </si>
   <si>
     <t xml:space="preserve">Brand 1</t>
@@ -258,23 +258,23 @@
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:V1048576"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.89"/>
@@ -282,13 +282,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.28"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="17.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="42.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="0" width="23.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="18" style="0" width="8.91"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -357,7 +356,7 @@
       </c>
       <c r="V1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>21</v>
       </c>
